--- a/docs/1. 项目工作计划-11组.xlsx
+++ b/docs/1. 项目工作计划-11组.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="72">
   <si>
     <t>山东理工大学-计算机科学与技术学院-软件工程系</t>
   </si>
@@ -110,7 +110,7 @@
     <t>系统总体结构设计，划分功能模块</t>
   </si>
   <si>
-    <t>Spring Boot + Vue</t>
+    <t>Spring Boot + React</t>
   </si>
   <si>
     <t>数据库设计</t>
@@ -137,7 +137,7 @@
     <t>张涵宇、马新皓</t>
   </si>
   <si>
-    <t>RESTful API + Vue</t>
+    <t>RESTful API + React</t>
   </si>
   <si>
     <t>确定模块间详细接口</t>
@@ -152,7 +152,7 @@
     <t>实现</t>
   </si>
   <si>
-    <t>框架搭建（Spring Boot + Vue + MySQL）</t>
+    <t>框架搭建（Spring Boot + React + MySQL）</t>
   </si>
   <si>
     <t>基础环境+项目骨架</t>
@@ -1607,9 +1607,7 @@
       <c r="H10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="I10" s="7"/>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:9">
       <c r="A11" s="12"/>
